--- a/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_parts_list_clean_v1_20260416.xlsx
+++ b/deliverables/bilal_ganj_master_market_pack_v17_20260416_032251/j40_parts_list_clean_v1_20260416.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2976,17 +2976,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fuse box - Compact covered ATO/ATC fuse block 6-way</t>
+          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>3 identical</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor fuse boxes or new compact covered aftermarket</t>
+          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PKR 11100-21000</t>
+          <t>PKR 54000-136000</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3011,22 +3011,22 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Covered body, firm lid, strong terminals</t>
+          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>229</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Reuse original Toyota-style boxes only if terminals are tight and no heat damage.</t>
+          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3048,17 +3048,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EPS kit - Complete EPS column kit with ECU, shafts, U-joints, couplers, brackets, connectors</t>
+          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>Full set</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor EPS column set (Bilal Ganj: Prius/Corolla/Vitz candidates)</t>
+          <t>New parts market only (no used donor plugs)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3068,37 +3068,37 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>PKR 54000-136000</t>
+          <t>PKR 12000-36000</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260317_235150.jpg</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>BUY_IF_ENGINE_CODE_MATCH</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Bench-test smooth assist; no lash/noise; pigtails &gt;=150mm</t>
+          <t>New only; no used/refurbished plugs</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260317_235150.jpg</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>N/A upgrade choice. Existing steering can stay if skipping EPS; EPS is optional improvement.</t>
+          <t>No. Glow/heat plugs should be new only.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3120,17 +3120,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Heat plugs / glow plugs - Diesel glow plug set (thread/reach/voltage per engine code)</t>
+          <t>Local front leaf spring pack (new fabricated) - measure eye-eye, width, arch, center pin, bush ID, eye width</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Full set</t>
+          <t>2 packs</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>New parts market only (no used donor plugs)</t>
+          <t>Local spring fabricator / suspension shop (not donor)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3140,47 +3140,47 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>PKR 12000-36000</t>
+          <t>PKR 35000-90000</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>images/20260317_235150.jpg</t>
+          <t>images/20260324_004852.jpg</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>BUY_IF_ENGINE_CODE_MATCH</t>
+          <t>MEASURE_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>New only; no used/refurbished plugs</t>
+          <t>Buy only after measured fit confirmation</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20260317_235150.jpg</t>
+          <t>20260324_004852.jpg;20260411_220207.jpg</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>No. Glow/heat plugs should be new only.</t>
+          <t>Maybe. Keep existing only if no cracks, no sag, and bush eyes are within tolerance after mechanic inspection.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>MEASURE_FIRST_THEN_BUY</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Unchanged from active parts list.</t>
+          <t>Active local front leaf spring path.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Local front leaf spring pack (new fabricated) - measure eye-eye, width, arch, center pin, bush ID, eye width</t>
+          <t>Local rear leaf spring pack (new fabricated) - measure eye-eye, width, arch, center pin, bush ID, eye width</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3232,17 +3232,17 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220207.jpg</t>
+          <t>20260324_004852.jpg;20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Keep existing only if no cracks, no sag, and bush eyes are within tolerance after mechanic inspection.</t>
+          <t>Maybe. Keep existing only if no cracks, no inversion risk, and ride height is acceptable after load check.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Active local front leaf spring path.</t>
+          <t>Active local rear leaf spring path.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3264,17 +3264,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Local rear leaf spring pack (new fabricated) - measure eye-eye, width, arch, center pin, bush ID, eye width</t>
+          <t>Steering bushings - Steering linkage bush set</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2 packs</t>
+          <t>1 set</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Local spring fabricator / suspension shop (not donor)</t>
+          <t>New hardware/electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3284,47 +3284,47 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>PKR 35000-90000</t>
+          <t>PKR 3000-12000</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>images/20260324_004852.jpg</t>
+          <t>images/20260406_031010.jpg</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_THEN_BUY_ACTIVE</t>
+          <t>INSPECT_THEN_BUY_ACTIVE</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Buy only after measured fit confirmation</t>
+          <t>Condition-based quote</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20260324_004852.jpg;20260411_220214.jpg</t>
+          <t>20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>230</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Keep existing only if no cracks, no inversion risk, and ride height is acceptable after load check.</t>
+          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>MEASURE_FIRST_THEN_BUY</t>
+          <t>BUY_ONLY_IF_PLAY_FOUND</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Active local rear leaf spring path.</t>
+          <t>Steering bushing only if wear/play confirmed.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3336,17 +3336,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushings - Steering linkage bush set</t>
+          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1 set</t>
+          <t>3 segments</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>New hardware/electrical market (not donor car)</t>
+          <t>Electrical workshop service (rework existing wires)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3356,47 +3356,47 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000</t>
+          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>images/20260406_031010.jpg</t>
+          <t>images/20260411_065030.jpg</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>INSPECT_THEN_BUY_ACTIVE</t>
+          <t>WORKSHOP_TASK</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Condition-based quote</t>
+          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20260406_031010.jpg</t>
+          <t>20260411_065030.jpg;20260321_235600.jpg</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>Electrical_Master</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Maybe. Replace only if measurable play, cracking, or steering looseness persists after service.</t>
+          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>BUY_ONLY_IF_PLAY_FOUND</t>
+          <t>AS_LISTED</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Steering bushing only if wear/play confirmed.</t>
+          <t>Unchanged from active parts list.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3408,27 +3408,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Wire rework - Split overlength heavy feed wire into 3 serviceable segments</t>
+          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>3 segments</t>
+          <t>10 rolls</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Electrical workshop service (rework existing wires)</t>
+          <t>New electrical market (not donor car)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>PKR 3000-12000 (labor + lugs/heat-shrink re-termination)</t>
+          <t>PKR 1500-4500</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3438,27 +3438,27 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP_TASK</t>
+          <t>BUY_NOW</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Cut+terminate+heat-shrink+continuity/voltage-drop test</t>
+          <t>Good adhesive and heat tolerance, not brittle PVC</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg;20260321_235600.jpg</t>
+          <t>20260411_065030.jpg</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Electrical_Master</t>
+          <t>SUB-17</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Yes. Rework existing overlength cable by cutting into 3 segments and re-terminating.</t>
+          <t>N/A consumable item; buy new.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Electrical tape (automotive PVC, 19mm x 18-20m)</t>
+          <t>Cloth harness loom tape (Tesa-style)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>10 rolls</t>
+          <t>5 rolls</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>PKR 1500-4500</t>
+          <t>PKR 2500-9000</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Good adhesive and heat tolerance, not brittle PVC</t>
+          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>SUB-17</t>
+          <t>SUB-23</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Cloth harness loom tape (Tesa-style)</t>
+          <t>Firewall grommet assortment</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>5 rolls</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>PKR 2500-9000</t>
+          <t>PKR 2000-7000</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_065030.jpg</t>
+          <t>images/20260411_143135.jpg</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3587,17 +3587,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Automotive-grade cloth tape; abrasion and heat resistance</t>
+          <t>Hole ID/OD fit and thickness for firewall panels</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20260411_065030.jpg</t>
+          <t>20260411_143135.jpg</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>SUB-23</t>
+          <t>SUB-11</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3624,17 +3624,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Firewall grommet assortment</t>
+          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1 kit</t>
+          <t>1 complete kit</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>New electrical market (not donor car)</t>
+          <t>Toyota donor car (Bilal Ganj)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3644,37 +3644,37 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PKR 2000-7000</t>
+          <t>PKR 60000-150000</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>images/20260411_143135.jpg</t>
+          <t>images/20260321_235600.jpg</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>BUY_NOW</t>
+          <t>QUOTE_ONLY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Hole ID/OD fit and thickness for firewall panels</t>
+          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20260411_143135.jpg</t>
+          <t>20260321_235600.jpg;20260406_031010.jpg</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>SUB-11</t>
+          <t>229-C1</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>N/A consumable item; buy new.</t>
+          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Prius column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>PKR 60000-150000</t>
+          <t>PKR 55000-140000</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Motor smooth assist, ECU + shafts + U-joints + couplers + brackets + pigtails included</t>
+          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>229-C1</t>
+          <t>229-C2</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Corolla/Axio column assist set (complete kit)</t>
+          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PKR 55000-140000</t>
+          <t>PKR 50000-130000</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>No lash/noise, compatible column length, complete ECU/connectors/shafts</t>
+          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>229-C2</t>
+          <t>229-C3</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3840,17 +3840,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EPS donor candidate - Toyota Vitz/Yaris column assist set (complete kit)</t>
+          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1 complete kit</t>
+          <t>1 kit</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Toyota donor car (Bilal Ganj)</t>
+          <t>OME/EMU supplier or suspension fabricator</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3860,122 +3860,50 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PKR 50000-130000</t>
+          <t>PKR 12000-35000</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>images/20260321_235600.jpg</t>
+          <t>images/20260411_220214.jpg</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>QUOTE_ONLY</t>
+          <t>CONDITIONAL_LOCAL_ACTIVE</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Column mount and spline compatibility; complete wiring pigtails and couplers</t>
+          <t>Bracket geometry for your rear spring setup and axle travel clearance</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20260321_235600.jpg;20260406_031010.jpg</t>
+          <t>20260411_220214.jpg</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>229-C3</t>
+          <t>SUS-10</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>N/A candidate option. Buy only if complete kit passes mechanic inspection and fit checks.</t>
+          <t>Maybe. If current rear springs show no inversion tendency, can defer this item.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>AS_LISTED</t>
+          <t>BUY_ONLY_IF_INVERSION_RISK</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Unchanged from active parts list.</t>
+          <t>Only needed if spring inversion tendency appears.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>KEPT_IN_ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Rear anti-inversion kit - FK08 (spring flip prevention)</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>1 kit</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>OME/EMU supplier or suspension fabricator</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>PKR 12000-35000</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>images/20260411_220214.jpg</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>CONDITIONAL_LOCAL_ACTIVE</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Bracket geometry for your rear spring setup and axle travel clearance</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>20260411_220214.jpg</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>SUS-10</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Maybe. If current rear springs show no inversion tendency, can defer this item.</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>BUY_ONLY_IF_INVERSION_RISK</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Only needed if spring inversion tendency appears.</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>KEPT_IN_ACTIVE</t>
         </is>
